--- a/output/pdf_financials_xlsx/SNDL.xlsx
+++ b/output/pdf_financials_xlsx/SNDL.xlsx
@@ -431,6 +431,13 @@
   </sheetPr>
   <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/SNDL.xlsx
+++ b/output/pdf_financials_xlsx/SNDL.xlsx
@@ -2795,16 +2795,16 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>1.213</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.734</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="113">
@@ -6792,7 +6792,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -7512,7 +7516,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -8658,7 +8666,11 @@
           <t>Additions to intangible assets 17</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E149" s="5" t="n">
         <v>-0.197</v>
       </c>
@@ -8760,7 +8772,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E152" s="5" t="n">
         <v>4</v>
       </c>

--- a/output/pdf_financials_xlsx/SNDL.xlsx
+++ b/output/pdf_financials_xlsx/SNDL.xlsx
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>7.342</v>
+        <v>-7.342</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-4.535</v>
@@ -866,7 +866,7 @@
         <v>-372.428</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-176.551</v>
+        <v>-172.016</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-4.535</v>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
@@ -1252,10 +1252,8 @@
       <c r="D37" s="3" t="n">
         <v>28.118</v>
       </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E37" s="3" t="n">
+        <v>24.096</v>
       </c>
     </row>
     <row r="38">
@@ -1307,18 +1305,16 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>5.078</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>6.21</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.57</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>3.547</v>
       </c>
     </row>
     <row r="41">
@@ -1328,13 +1324,13 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>22.636</v>
+        <v>27.714</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>27.059</v>
+        <v>33.269</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>28.118</v>
+        <v>31.688</v>
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
@@ -1475,13 +1471,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>49.553</v>
+        <v>44.475</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>55.529</v>
+        <v>49.319</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>87.30500000000001</v>
+        <v>83.735</v>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
@@ -1817,18 +1813,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>9.773999999999999</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>22.035</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>27.064</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>28.006</v>
       </c>
     </row>
     <row r="65">
@@ -1943,13 +1937,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>30.206</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>30.537</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>34.256</v>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
@@ -1964,13 +1958,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>30.206</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>30.537</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>34.256</v>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
@@ -2048,13 +2042,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>41.208</v>
+        <v>11.002</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>34.937</v>
+        <v>4.4</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>34.282</v>
+        <v>0.026</v>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
@@ -2153,13 +2147,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>0.1051666283786074</v>
+        <v>0.127918020871386</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.1110286820570387</v>
+        <v>0.1358688401906714</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.1041305644475346</v>
+        <v>0.1343558422949188</v>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
@@ -2855,13 +2849,13 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>6.704</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="116">
@@ -4290,7 +4284,11 @@
           <t>Lease liabilities 21 35,462</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -5552,7 +5550,11 @@
           <t>Lease liabilities 23</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>30.206</v>
       </c>
@@ -6686,7 +6688,11 @@
           <t>Proceeds from disposal of investments 16</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -7338,7 +7344,11 @@
           <t>Proceeds from settlement of marketable securities 9</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -8340,7 +8350,11 @@
           <t>Proceeds from settlement of marketable securities 9</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -11774,7 +11788,11 @@
           <t>Income tax recovery 25</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E242" s="5" t="n">
         <v>7.342</v>
       </c>
@@ -11806,7 +11824,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E243" s="5" t="n">
         <v>-372.428</v>
       </c>
@@ -11836,7 +11858,11 @@
           <t>Net loss from discontinued operations 6</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
